--- a/data/samples/reports/sample_data/dashboard.xlsx
+++ b/data/samples/reports/sample_data/dashboard.xlsx
@@ -76,7 +76,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="7620000" cy="4762500"/>
+    <xdr:ext cx="18288000" cy="10287000"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="" descr=""/>
@@ -114,7 +114,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="7620000" cy="4762500"/>
+    <xdr:ext cx="18288000" cy="10287000"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="" descr=""/>
@@ -152,7 +152,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="7620000" cy="4762500"/>
+    <xdr:ext cx="18288000" cy="10287000"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="" descr=""/>
@@ -190,7 +190,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="7620000" cy="4762500"/>
+    <xdr:ext cx="18288000" cy="10287000"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="" descr=""/>
@@ -228,7 +228,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="7620000" cy="4762500"/>
+    <xdr:ext cx="18288000" cy="10287000"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="" descr=""/>
@@ -1128,7 +1128,7 @@
   <sheetCalcPr fullCalcOnLoad="1"/>
   <printOptions gridLines="0" headings="0" horizontalCentered="0" verticalCentered="0"/>
   <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.5" footer="0.5"/>
-  <pageSetup/>
+  <pageSetup orientation="landscape"/>
   <headerFooter/>
   <drawing r:id="rId13"/>
 </worksheet>
@@ -1144,7 +1144,7 @@
   <sheetCalcPr fullCalcOnLoad="1"/>
   <printOptions gridLines="0" headings="0" horizontalCentered="0" verticalCentered="0"/>
   <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.5" footer="0.5"/>
-  <pageSetup/>
+  <pageSetup orientation="landscape"/>
   <headerFooter/>
   <drawing r:id="rId14"/>
 </worksheet>
@@ -1160,7 +1160,7 @@
   <sheetCalcPr fullCalcOnLoad="1"/>
   <printOptions gridLines="0" headings="0" horizontalCentered="0" verticalCentered="0"/>
   <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.5" footer="0.5"/>
-  <pageSetup/>
+  <pageSetup orientation="landscape"/>
   <headerFooter/>
   <drawing r:id="rId15"/>
 </worksheet>
@@ -1176,7 +1176,7 @@
   <sheetCalcPr fullCalcOnLoad="1"/>
   <printOptions gridLines="0" headings="0" horizontalCentered="0" verticalCentered="0"/>
   <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.5" footer="0.5"/>
-  <pageSetup/>
+  <pageSetup orientation="landscape"/>
   <headerFooter/>
   <drawing r:id="rId16"/>
 </worksheet>
@@ -1192,7 +1192,7 @@
   <sheetCalcPr fullCalcOnLoad="1"/>
   <printOptions gridLines="0" headings="0" horizontalCentered="0" verticalCentered="0"/>
   <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.5" footer="0.5"/>
-  <pageSetup/>
+  <pageSetup orientation="landscape"/>
   <headerFooter/>
   <drawing r:id="rId17"/>
 </worksheet>

--- a/data/samples/reports/sample_data/dashboard.xlsx
+++ b/data/samples/reports/sample_data/dashboard.xlsx
@@ -4,11 +4,6 @@
   <workbookPr date1904="false"/>
   <sheets>
     <sheet sheetId="1" name="Work Items" r:id="rId1"/>
-    <sheet sheetId="2" name="Aging Wip" r:id="rId2"/>
-    <sheet sheetId="3" name="Cfd Plot" r:id="rId3"/>
-    <sheet sheetId="4" name="Cycle Time Scatter" r:id="rId4"/>
-    <sheet sheetId="5" name="Forecasted Cfd Plot" r:id="rId5"/>
-    <sheet sheetId="6" name="Throughput Histogram" r:id="rId6"/>
   </sheets>
 </workbook>
 </file>
@@ -67,196 +62,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="18288000" cy="10287000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="" descr=""/>
-        <xdr:cNvPicPr>
-          <a:picLocks noSelect="1" noChangeAspect="1" noMove="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="2336800" cy="2161540"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="18288000" cy="10287000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="" descr=""/>
-        <xdr:cNvPicPr>
-          <a:picLocks noSelect="1" noChangeAspect="1" noMove="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="2336800" cy="2161540"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="18288000" cy="10287000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="" descr=""/>
-        <xdr:cNvPicPr>
-          <a:picLocks noSelect="1" noChangeAspect="1" noMove="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="2336800" cy="2161540"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="18288000" cy="10287000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="" descr=""/>
-        <xdr:cNvPicPr>
-          <a:picLocks noSelect="1" noChangeAspect="1" noMove="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="2336800" cy="2161540"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="18288000" cy="10287000"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="" descr=""/>
-        <xdr:cNvPicPr>
-          <a:picLocks noSelect="1" noChangeAspect="1" noMove="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="2336800" cy="2161540"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-</xdr:wsDr>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
   <sheetPr>
@@ -1116,84 +921,4 @@
   <pageSetup/>
   <headerFooter/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <sheetPr>
-    <pageSetUpPr fitToPage="0"/>
-  </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
-  <sheetData/>
-  <sheetCalcPr fullCalcOnLoad="1"/>
-  <printOptions gridLines="0" headings="0" horizontalCentered="0" verticalCentered="0"/>
-  <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape"/>
-  <headerFooter/>
-  <drawing r:id="rId13"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <sheetPr>
-    <pageSetUpPr fitToPage="0"/>
-  </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
-  <sheetData/>
-  <sheetCalcPr fullCalcOnLoad="1"/>
-  <printOptions gridLines="0" headings="0" horizontalCentered="0" verticalCentered="0"/>
-  <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape"/>
-  <headerFooter/>
-  <drawing r:id="rId14"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <sheetPr>
-    <pageSetUpPr fitToPage="0"/>
-  </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
-  <sheetData/>
-  <sheetCalcPr fullCalcOnLoad="1"/>
-  <printOptions gridLines="0" headings="0" horizontalCentered="0" verticalCentered="0"/>
-  <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape"/>
-  <headerFooter/>
-  <drawing r:id="rId15"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <sheetPr>
-    <pageSetUpPr fitToPage="0"/>
-  </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
-  <sheetData/>
-  <sheetCalcPr fullCalcOnLoad="1"/>
-  <printOptions gridLines="0" headings="0" horizontalCentered="0" verticalCentered="0"/>
-  <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape"/>
-  <headerFooter/>
-  <drawing r:id="rId16"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <sheetPr>
-    <pageSetUpPr fitToPage="0"/>
-  </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
-  <sheetData/>
-  <sheetCalcPr fullCalcOnLoad="1"/>
-  <printOptions gridLines="0" headings="0" horizontalCentered="0" verticalCentered="0"/>
-  <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape"/>
-  <headerFooter/>
-  <drawing r:id="rId17"/>
-</worksheet>
 </file>
--- a/data/samples/reports/sample_data/dashboard.xlsx
+++ b/data/samples/reports/sample_data/dashboard.xlsx
@@ -4,6 +4,11 @@
   <workbookPr date1904="false"/>
   <sheets>
     <sheet sheetId="1" name="Work Items" r:id="rId1"/>
+    <sheet sheetId="2" name="Aging Wip" r:id="rId2"/>
+    <sheet sheetId="3" name="Cfd Plot" r:id="rId3"/>
+    <sheet sheetId="4" name="Cycle Time Scatter" r:id="rId4"/>
+    <sheet sheetId="5" name="Forecasted Cfd Plot" r:id="rId5"/>
+    <sheet sheetId="6" name="Throughput Histogram" r:id="rId6"/>
   </sheets>
 </workbook>
 </file>
@@ -62,6 +67,196 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="18288000" cy="10287000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="" descr=""/>
+        <xdr:cNvPicPr>
+          <a:picLocks noSelect="1" noChangeAspect="1" noMove="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2336800" cy="2161540"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="18288000" cy="10287000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="" descr=""/>
+        <xdr:cNvPicPr>
+          <a:picLocks noSelect="1" noChangeAspect="1" noMove="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2336800" cy="2161540"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="18288000" cy="10287000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="" descr=""/>
+        <xdr:cNvPicPr>
+          <a:picLocks noSelect="1" noChangeAspect="1" noMove="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2336800" cy="2161540"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="18288000" cy="10287000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="" descr=""/>
+        <xdr:cNvPicPr>
+          <a:picLocks noSelect="1" noChangeAspect="1" noMove="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2336800" cy="2161540"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="18288000" cy="10287000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="" descr=""/>
+        <xdr:cNvPicPr>
+          <a:picLocks noSelect="1" noChangeAspect="1" noMove="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2336800" cy="2161540"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
   <sheetPr>
@@ -921,4 +1116,84 @@
   <pageSetup/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
+  <sheetData/>
+  <sheetCalcPr fullCalcOnLoad="1"/>
+  <printOptions gridLines="0" headings="0" horizontalCentered="0" verticalCentered="0"/>
+  <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape"/>
+  <headerFooter/>
+  <drawing r:id="rId13"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
+  <sheetData/>
+  <sheetCalcPr fullCalcOnLoad="1"/>
+  <printOptions gridLines="0" headings="0" horizontalCentered="0" verticalCentered="0"/>
+  <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape"/>
+  <headerFooter/>
+  <drawing r:id="rId14"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
+  <sheetData/>
+  <sheetCalcPr fullCalcOnLoad="1"/>
+  <printOptions gridLines="0" headings="0" horizontalCentered="0" verticalCentered="0"/>
+  <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape"/>
+  <headerFooter/>
+  <drawing r:id="rId15"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
+  <sheetData/>
+  <sheetCalcPr fullCalcOnLoad="1"/>
+  <printOptions gridLines="0" headings="0" horizontalCentered="0" verticalCentered="0"/>
+  <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape"/>
+  <headerFooter/>
+  <drawing r:id="rId16"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
+  <sheetData/>
+  <sheetCalcPr fullCalcOnLoad="1"/>
+  <printOptions gridLines="0" headings="0" horizontalCentered="0" verticalCentered="0"/>
+  <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape"/>
+  <headerFooter/>
+  <drawing r:id="rId17"/>
+</worksheet>
 </file>
--- a/data/samples/reports/sample_data/dashboard.xlsx
+++ b/data/samples/reports/sample_data/dashboard.xlsx
@@ -6,9 +6,10 @@
     <sheet sheetId="1" name="Work Items" r:id="rId1"/>
     <sheet sheetId="2" name="Aging Wip" r:id="rId2"/>
     <sheet sheetId="3" name="Cfd Plot" r:id="rId3"/>
-    <sheet sheetId="4" name="Cycle Time Scatter" r:id="rId4"/>
-    <sheet sheetId="5" name="Forecasted Cfd Plot" r:id="rId5"/>
-    <sheet sheetId="6" name="Throughput Histogram" r:id="rId6"/>
+    <sheet sheetId="4" name="Cycle Time Bands" r:id="rId4"/>
+    <sheet sheetId="5" name="Cycle Time Scatter" r:id="rId5"/>
+    <sheet sheetId="6" name="Forecasted Cfd Plot" r:id="rId6"/>
+    <sheet sheetId="7" name="Throughput Histogram" r:id="rId7"/>
   </sheets>
 </workbook>
 </file>
@@ -76,7 +77,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="18288000" cy="10287000"/>
+    <xdr:ext cx="5038725" cy="4667250"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="" descr=""/>
@@ -85,7 +86,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -114,7 +115,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="18288000" cy="10287000"/>
+    <xdr:ext cx="5038725" cy="4667250"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="" descr=""/>
@@ -123,7 +124,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -152,7 +153,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="18288000" cy="10287000"/>
+    <xdr:ext cx="5038725" cy="4667250"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="" descr=""/>
@@ -161,7 +162,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -190,7 +191,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="18288000" cy="10287000"/>
+    <xdr:ext cx="5038725" cy="4667250"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="" descr=""/>
@@ -199,7 +200,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -228,7 +229,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="18288000" cy="10287000"/>
+    <xdr:ext cx="5038725" cy="4667250"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="" descr=""/>
@@ -237,7 +238,45 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2336800" cy="2161540"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="5038725" cy="4667250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="" descr=""/>
+        <xdr:cNvPicPr>
+          <a:picLocks noSelect="1" noChangeAspect="1" noMove="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -262,7 +301,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:N19"/>
+  <dimension ref="A1:Q19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="11.0" min="1" max="1" bestFit="1" customWidth="1"/>
@@ -272,13 +311,16 @@
     <col width="14.3" min="5" max="5" bestFit="1" customWidth="1"/>
     <col width="14.3" min="6" max="6" bestFit="1" customWidth="1"/>
     <col width="15.400000000000002" min="7" max="7" bestFit="1" customWidth="1"/>
-    <col width="22.0" min="8" max="8" bestFit="1" customWidth="1"/>
-    <col width="23.1" min="9" max="9" bestFit="1" customWidth="1"/>
-    <col width="16.5" min="10" max="10" bestFit="1" customWidth="1"/>
-    <col width="17.6" min="11" max="11" bestFit="1" customWidth="1"/>
-    <col width="18.700000000000003" min="12" max="12" bestFit="1" customWidth="1"/>
-    <col width="18.700000000000003" min="13" max="13" bestFit="1" customWidth="1"/>
-    <col width="18.700000000000003" min="14" max="14" bestFit="1" customWidth="1"/>
+    <col width="13.200000000000001" min="8" max="8" bestFit="1" customWidth="1"/>
+    <col width="11.0" min="9" max="9" bestFit="1" customWidth="1"/>
+    <col width="7.700000000000001" min="10" max="10" bestFit="1" customWidth="1"/>
+    <col width="22.0" min="11" max="11" bestFit="1" customWidth="1"/>
+    <col width="23.1" min="12" max="12" bestFit="1" customWidth="1"/>
+    <col width="16.5" min="13" max="13" bestFit="1" customWidth="1"/>
+    <col width="17.6" min="14" max="14" bestFit="1" customWidth="1"/>
+    <col width="18.700000000000003" min="15" max="15" bestFit="1" customWidth="1"/>
+    <col width="18.700000000000003" min="16" max="16" bestFit="1" customWidth="1"/>
+    <col width="18.700000000000003" min="17" max="17" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -319,35 +361,50 @@
       </c>
       <c r="H1" s="0" t="inlineStr">
         <is>
+          <t>YYYY-Week</t>
+        </is>
+      </c>
+      <c r="I1" s="0" t="inlineStr">
+        <is>
+          <t>YYYY-MM</t>
+        </is>
+      </c>
+      <c r="J1" s="0" t="inlineStr">
+        <is>
+          <t>YYYY</t>
+        </is>
+      </c>
+      <c r="K1" s="0" t="inlineStr">
+        <is>
           <t>Cycle Time (days)</t>
         </is>
       </c>
-      <c r="I1" s="0" t="inlineStr">
+      <c r="L1" s="0" t="inlineStr">
         <is>
           <t>Current Age (days)</t>
         </is>
       </c>
-      <c r="J1" s="0" t="inlineStr">
+      <c r="M1" s="0" t="inlineStr">
         <is>
           <t>Done ≤ 1 day</t>
         </is>
       </c>
-      <c r="K1" s="0" t="inlineStr">
+      <c r="N1" s="0" t="inlineStr">
         <is>
           <t>Done ≤ 7 days</t>
         </is>
       </c>
-      <c r="L1" s="0" t="inlineStr">
+      <c r="O1" s="0" t="inlineStr">
         <is>
           <t>Done ≤ 14 days</t>
         </is>
       </c>
-      <c r="M1" s="0" t="inlineStr">
+      <c r="P1" s="0" t="inlineStr">
         <is>
           <t>Done ≤ 21 days</t>
         </is>
       </c>
-      <c r="N1" s="0" t="inlineStr">
+      <c r="Q1" s="0" t="inlineStr">
         <is>
           <t>Done ≤ 28 days</t>
         </is>
@@ -377,23 +434,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H2" s="0" t="n">
+      <c r="H2" s="0" t="inlineStr">
+        <is>
+          <t>2026-W10</t>
+        </is>
+      </c>
+      <c r="I2" s="0" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="J2" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K2" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="I2" s="0"/>
-      <c r="J2" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K2" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="L2" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L2" s="0"/>
       <c r="M2" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N2" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="O2" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P2" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -421,23 +491,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H3" s="0" t="n">
+      <c r="H3" s="0" t="inlineStr">
+        <is>
+          <t>2026-W10</t>
+        </is>
+      </c>
+      <c r="I3" s="0" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="J3" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K3" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="I3" s="0"/>
-      <c r="J3" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K3" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="L3" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L3" s="0"/>
       <c r="M3" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N3" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="O3" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P3" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -465,23 +548,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H4" s="0" t="n">
+      <c r="H4" s="0" t="inlineStr">
+        <is>
+          <t>2026-W11</t>
+        </is>
+      </c>
+      <c r="I4" s="0" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="J4" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K4" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="I4" s="0"/>
-      <c r="J4" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K4" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="L4" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L4" s="0"/>
       <c r="M4" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N4" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="O4" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P4" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -509,23 +605,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H5" s="0" t="n">
+      <c r="H5" s="0" t="inlineStr">
+        <is>
+          <t>2026-W10</t>
+        </is>
+      </c>
+      <c r="I5" s="0" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="J5" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K5" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="I5" s="0"/>
-      <c r="J5" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K5" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="L5" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L5" s="0"/>
       <c r="M5" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N5" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="O5" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P5" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -553,23 +662,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H6" s="0" t="n">
+      <c r="H6" s="0" t="inlineStr">
+        <is>
+          <t>2026-W11</t>
+        </is>
+      </c>
+      <c r="I6" s="0" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="J6" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K6" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="I6" s="0"/>
-      <c r="J6" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K6" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="L6" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L6" s="0"/>
       <c r="M6" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N6" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="O6" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P6" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -597,23 +719,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H7" s="0" t="n">
+      <c r="H7" s="0" t="inlineStr">
+        <is>
+          <t>2026-W11</t>
+        </is>
+      </c>
+      <c r="I7" s="0" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="J7" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K7" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="I7" s="0"/>
-      <c r="J7" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K7" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="L7" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L7" s="0"/>
       <c r="M7" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N7" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="O7" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P7" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -641,23 +776,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H8" s="0" t="n">
+      <c r="H8" s="0" t="inlineStr">
+        <is>
+          <t>2026-W12</t>
+        </is>
+      </c>
+      <c r="I8" s="0" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="J8" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K8" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="I8" s="0"/>
-      <c r="J8" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K8" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="L8" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L8" s="0"/>
       <c r="M8" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="O8" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P8" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -685,23 +833,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H9" s="0" t="n">
+      <c r="H9" s="0" t="inlineStr">
+        <is>
+          <t>2026-W12</t>
+        </is>
+      </c>
+      <c r="I9" s="0" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="J9" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K9" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="I9" s="0"/>
-      <c r="J9" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K9" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="L9" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L9" s="0"/>
       <c r="M9" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N9" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="O9" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P9" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -729,23 +890,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H10" s="0" t="n">
+      <c r="H10" s="0" t="inlineStr">
+        <is>
+          <t>2026-W12</t>
+        </is>
+      </c>
+      <c r="I10" s="0" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="J10" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K10" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="I10" s="0"/>
-      <c r="J10" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K10" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="L10" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L10" s="0"/>
       <c r="M10" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N10" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="O10" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P10" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -773,23 +947,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H11" s="0" t="n">
+      <c r="H11" s="0" t="inlineStr">
+        <is>
+          <t>2026-W13</t>
+        </is>
+      </c>
+      <c r="I11" s="0" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="J11" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K11" s="0" t="n">
         <v>8</v>
       </c>
-      <c r="I11" s="0"/>
-      <c r="J11" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K11" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L11" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L11" s="0"/>
       <c r="M11" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N11" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O11" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P11" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q11" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -817,23 +1004,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H12" s="0" t="n">
+      <c r="H12" s="0" t="inlineStr">
+        <is>
+          <t>2026-W13</t>
+        </is>
+      </c>
+      <c r="I12" s="0" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="J12" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K12" s="0" t="n">
         <v>9</v>
       </c>
-      <c r="I12" s="0"/>
-      <c r="J12" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K12" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L12" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L12" s="0"/>
       <c r="M12" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O12" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P12" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q12" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -861,23 +1061,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H13" s="0" t="n">
+      <c r="H13" s="0" t="inlineStr">
+        <is>
+          <t>2026-W14</t>
+        </is>
+      </c>
+      <c r="I13" s="0" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="J13" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K13" s="0" t="n">
         <v>11</v>
       </c>
-      <c r="I13" s="0"/>
-      <c r="J13" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K13" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L13" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L13" s="0"/>
       <c r="M13" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N13" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O13" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P13" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q13" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -905,23 +1118,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H14" s="0" t="n">
+      <c r="H14" s="0" t="inlineStr">
+        <is>
+          <t>2026-W14</t>
+        </is>
+      </c>
+      <c r="I14" s="0" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="J14" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K14" s="0" t="n">
         <v>11</v>
       </c>
-      <c r="I14" s="0"/>
-      <c r="J14" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K14" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L14" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L14" s="0"/>
       <c r="M14" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N14" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O14" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P14" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q14" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -949,23 +1175,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H15" s="0" t="n">
+      <c r="H15" s="0" t="inlineStr">
+        <is>
+          <t>2026-W14</t>
+        </is>
+      </c>
+      <c r="I15" s="0" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="J15" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K15" s="0" t="n">
         <v>11</v>
       </c>
-      <c r="I15" s="0"/>
-      <c r="J15" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K15" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L15" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L15" s="0"/>
       <c r="M15" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N15" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O15" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P15" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q15" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -993,23 +1232,36 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="H16" s="0" t="n">
+      <c r="H16" s="0" t="inlineStr">
+        <is>
+          <t>2026-W15</t>
+        </is>
+      </c>
+      <c r="I16" s="0" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="J16" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K16" s="0" t="n">
         <v>12</v>
       </c>
-      <c r="I16" s="0"/>
-      <c r="J16" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="K16" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="L16" s="0" t="b">
-        <v>1</v>
-      </c>
+      <c r="L16" s="0"/>
       <c r="M16" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O16" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="P16" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q16" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1036,14 +1288,17 @@
         </is>
       </c>
       <c r="H17" s="0"/>
-      <c r="I17" s="0" t="n">
-        <v>32</v>
-      </c>
+      <c r="I17" s="0"/>
       <c r="J17" s="0"/>
       <c r="K17" s="0"/>
-      <c r="L17" s="0"/>
+      <c r="L17" s="0" t="n">
+        <v>33</v>
+      </c>
       <c r="M17" s="0"/>
       <c r="N17" s="0"/>
+      <c r="O17" s="0"/>
+      <c r="P17" s="0"/>
+      <c r="Q17" s="0"/>
     </row>
     <row r="18">
       <c r="A18" s="0" t="inlineStr">
@@ -1068,14 +1323,17 @@
         </is>
       </c>
       <c r="H18" s="0"/>
-      <c r="I18" s="0" t="n">
-        <v>30</v>
-      </c>
+      <c r="I18" s="0"/>
       <c r="J18" s="0"/>
       <c r="K18" s="0"/>
-      <c r="L18" s="0"/>
+      <c r="L18" s="0" t="n">
+        <v>31</v>
+      </c>
       <c r="M18" s="0"/>
       <c r="N18" s="0"/>
+      <c r="O18" s="0"/>
+      <c r="P18" s="0"/>
+      <c r="Q18" s="0"/>
     </row>
     <row r="19">
       <c r="A19" s="0" t="inlineStr">
@@ -1100,14 +1358,17 @@
         </is>
       </c>
       <c r="H19" s="0"/>
-      <c r="I19" s="0" t="n">
-        <v>28</v>
-      </c>
+      <c r="I19" s="0"/>
       <c r="J19" s="0"/>
       <c r="K19" s="0"/>
-      <c r="L19" s="0"/>
+      <c r="L19" s="0" t="n">
+        <v>29</v>
+      </c>
       <c r="M19" s="0"/>
       <c r="N19" s="0"/>
+      <c r="O19" s="0"/>
+      <c r="P19" s="0"/>
+      <c r="Q19" s="0"/>
     </row>
   </sheetData>
   <sheetCalcPr fullCalcOnLoad="1"/>
@@ -1130,7 +1391,7 @@
   <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
   <headerFooter/>
-  <drawing r:id="rId13"/>
+  <drawing r:id="rId15"/>
 </worksheet>
 </file>
 
@@ -1146,7 +1407,7 @@
   <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
   <headerFooter/>
-  <drawing r:id="rId14"/>
+  <drawing r:id="rId16"/>
 </worksheet>
 </file>
 
@@ -1162,7 +1423,7 @@
   <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
   <headerFooter/>
-  <drawing r:id="rId15"/>
+  <drawing r:id="rId17"/>
 </worksheet>
 </file>
 
@@ -1178,7 +1439,7 @@
   <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
   <headerFooter/>
-  <drawing r:id="rId16"/>
+  <drawing r:id="rId18"/>
 </worksheet>
 </file>
 
@@ -1194,6 +1455,22 @@
   <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
   <headerFooter/>
-  <drawing r:id="rId17"/>
+  <drawing r:id="rId19"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
+  <sheetData/>
+  <sheetCalcPr fullCalcOnLoad="1"/>
+  <printOptions gridLines="0" headings="0" horizontalCentered="0" verticalCentered="0"/>
+  <pageMargins left="0.75" right="0.75" top="1.0" bottom="1.0" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape"/>
+  <headerFooter/>
+  <drawing r:id="rId20"/>
 </worksheet>
 </file>
--- a/data/samples/reports/sample_data/dashboard.xlsx
+++ b/data/samples/reports/sample_data/dashboard.xlsx
@@ -1292,7 +1292,7 @@
       <c r="J17" s="0"/>
       <c r="K17" s="0"/>
       <c r="L17" s="0" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M17" s="0"/>
       <c r="N17" s="0"/>
@@ -1327,7 +1327,7 @@
       <c r="J18" s="0"/>
       <c r="K18" s="0"/>
       <c r="L18" s="0" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M18" s="0"/>
       <c r="N18" s="0"/>
@@ -1362,7 +1362,7 @@
       <c r="J19" s="0"/>
       <c r="K19" s="0"/>
       <c r="L19" s="0" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M19" s="0"/>
       <c r="N19" s="0"/>

--- a/data/samples/reports/sample_data/dashboard.xlsx
+++ b/data/samples/reports/sample_data/dashboard.xlsx
@@ -1292,7 +1292,7 @@
       <c r="J17" s="0"/>
       <c r="K17" s="0"/>
       <c r="L17" s="0" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M17" s="0"/>
       <c r="N17" s="0"/>
@@ -1327,7 +1327,7 @@
       <c r="J18" s="0"/>
       <c r="K18" s="0"/>
       <c r="L18" s="0" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M18" s="0"/>
       <c r="N18" s="0"/>
@@ -1362,7 +1362,7 @@
       <c r="J19" s="0"/>
       <c r="K19" s="0"/>
       <c r="L19" s="0" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M19" s="0"/>
       <c r="N19" s="0"/>

--- a/data/samples/reports/sample_data/dashboard.xlsx
+++ b/data/samples/reports/sample_data/dashboard.xlsx
@@ -1292,7 +1292,7 @@
       <c r="J17" s="0"/>
       <c r="K17" s="0"/>
       <c r="L17" s="0" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M17" s="0"/>
       <c r="N17" s="0"/>
@@ -1327,7 +1327,7 @@
       <c r="J18" s="0"/>
       <c r="K18" s="0"/>
       <c r="L18" s="0" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M18" s="0"/>
       <c r="N18" s="0"/>
@@ -1362,7 +1362,7 @@
       <c r="J19" s="0"/>
       <c r="K19" s="0"/>
       <c r="L19" s="0" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M19" s="0"/>
       <c r="N19" s="0"/>

--- a/data/samples/reports/sample_data/dashboard.xlsx
+++ b/data/samples/reports/sample_data/dashboard.xlsx
@@ -1292,7 +1292,7 @@
       <c r="J17" s="0"/>
       <c r="K17" s="0"/>
       <c r="L17" s="0" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M17" s="0"/>
       <c r="N17" s="0"/>
@@ -1327,7 +1327,7 @@
       <c r="J18" s="0"/>
       <c r="K18" s="0"/>
       <c r="L18" s="0" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M18" s="0"/>
       <c r="N18" s="0"/>
@@ -1362,7 +1362,7 @@
       <c r="J19" s="0"/>
       <c r="K19" s="0"/>
       <c r="L19" s="0" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M19" s="0"/>
       <c r="N19" s="0"/>

--- a/data/samples/reports/sample_data/dashboard.xlsx
+++ b/data/samples/reports/sample_data/dashboard.xlsx
@@ -1292,7 +1292,7 @@
       <c r="J17" s="0"/>
       <c r="K17" s="0"/>
       <c r="L17" s="0" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M17" s="0"/>
       <c r="N17" s="0"/>
@@ -1327,7 +1327,7 @@
       <c r="J18" s="0"/>
       <c r="K18" s="0"/>
       <c r="L18" s="0" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M18" s="0"/>
       <c r="N18" s="0"/>
@@ -1362,7 +1362,7 @@
       <c r="J19" s="0"/>
       <c r="K19" s="0"/>
       <c r="L19" s="0" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M19" s="0"/>
       <c r="N19" s="0"/>

--- a/data/samples/reports/sample_data/dashboard.xlsx
+++ b/data/samples/reports/sample_data/dashboard.xlsx
@@ -1292,7 +1292,7 @@
       <c r="J17" s="0"/>
       <c r="K17" s="0"/>
       <c r="L17" s="0" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M17" s="0"/>
       <c r="N17" s="0"/>
@@ -1327,7 +1327,7 @@
       <c r="J18" s="0"/>
       <c r="K18" s="0"/>
       <c r="L18" s="0" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M18" s="0"/>
       <c r="N18" s="0"/>
@@ -1362,7 +1362,7 @@
       <c r="J19" s="0"/>
       <c r="K19" s="0"/>
       <c r="L19" s="0" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M19" s="0"/>
       <c r="N19" s="0"/>

--- a/data/samples/reports/sample_data/dashboard.xlsx
+++ b/data/samples/reports/sample_data/dashboard.xlsx
@@ -1292,7 +1292,7 @@
       <c r="J17" s="0"/>
       <c r="K17" s="0"/>
       <c r="L17" s="0" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M17" s="0"/>
       <c r="N17" s="0"/>
@@ -1327,7 +1327,7 @@
       <c r="J18" s="0"/>
       <c r="K18" s="0"/>
       <c r="L18" s="0" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M18" s="0"/>
       <c r="N18" s="0"/>
@@ -1362,7 +1362,7 @@
       <c r="J19" s="0"/>
       <c r="K19" s="0"/>
       <c r="L19" s="0" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M19" s="0"/>
       <c r="N19" s="0"/>

--- a/data/samples/reports/sample_data/dashboard.xlsx
+++ b/data/samples/reports/sample_data/dashboard.xlsx
@@ -301,7 +301,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:Q19"/>
+  <dimension ref="A1:R19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="11.0" min="1" max="1" bestFit="1" customWidth="1"/>
@@ -316,11 +316,12 @@
     <col width="7.700000000000001" min="10" max="10" bestFit="1" customWidth="1"/>
     <col width="22.0" min="11" max="11" bestFit="1" customWidth="1"/>
     <col width="23.1" min="12" max="12" bestFit="1" customWidth="1"/>
-    <col width="16.5" min="13" max="13" bestFit="1" customWidth="1"/>
-    <col width="17.6" min="14" max="14" bestFit="1" customWidth="1"/>
-    <col width="18.700000000000003" min="15" max="15" bestFit="1" customWidth="1"/>
+    <col width="92.4" min="13" max="13" bestFit="1" customWidth="1"/>
+    <col width="16.5" min="14" max="14" bestFit="1" customWidth="1"/>
+    <col width="17.6" min="15" max="15" bestFit="1" customWidth="1"/>
     <col width="18.700000000000003" min="16" max="16" bestFit="1" customWidth="1"/>
     <col width="18.700000000000003" min="17" max="17" bestFit="1" customWidth="1"/>
+    <col width="18.700000000000003" min="18" max="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -386,25 +387,30 @@
       </c>
       <c r="M1" s="0" t="inlineStr">
         <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="N1" s="0" t="inlineStr">
+        <is>
           <t>Done ≤ 1 day</t>
         </is>
       </c>
-      <c r="N1" s="0" t="inlineStr">
+      <c r="O1" s="0" t="inlineStr">
         <is>
           <t>Done ≤ 7 days</t>
         </is>
       </c>
-      <c r="O1" s="0" t="inlineStr">
+      <c r="P1" s="0" t="inlineStr">
         <is>
           <t>Done ≤ 14 days</t>
         </is>
       </c>
-      <c r="P1" s="0" t="inlineStr">
+      <c r="Q1" s="0" t="inlineStr">
         <is>
           <t>Done ≤ 21 days</t>
         </is>
       </c>
-      <c r="Q1" s="0" t="inlineStr">
+      <c r="R1" s="0" t="inlineStr">
         <is>
           <t>Done ≤ 28 days</t>
         </is>
@@ -451,11 +457,13 @@
         <v>5</v>
       </c>
       <c r="L2" s="0"/>
-      <c r="M2" s="0" t="b">
-        <v>0</v>
+      <c r="M2" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data.csv</t>
+        </is>
       </c>
       <c r="N2" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O2" s="0" t="b">
         <v>1</v>
@@ -464,6 +472,9 @@
         <v>1</v>
       </c>
       <c r="Q2" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R2" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -508,11 +519,13 @@
         <v>3</v>
       </c>
       <c r="L3" s="0"/>
-      <c r="M3" s="0" t="b">
-        <v>0</v>
+      <c r="M3" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data.csv</t>
+        </is>
       </c>
       <c r="N3" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O3" s="0" t="b">
         <v>1</v>
@@ -521,6 +534,9 @@
         <v>1</v>
       </c>
       <c r="Q3" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R3" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -565,11 +581,13 @@
         <v>6</v>
       </c>
       <c r="L4" s="0"/>
-      <c r="M4" s="0" t="b">
-        <v>0</v>
+      <c r="M4" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data.csv</t>
+        </is>
       </c>
       <c r="N4" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O4" s="0" t="b">
         <v>1</v>
@@ -578,6 +596,9 @@
         <v>1</v>
       </c>
       <c r="Q4" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R4" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -622,11 +643,13 @@
         <v>2</v>
       </c>
       <c r="L5" s="0"/>
-      <c r="M5" s="0" t="b">
-        <v>0</v>
+      <c r="M5" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data.csv</t>
+        </is>
       </c>
       <c r="N5" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O5" s="0" t="b">
         <v>1</v>
@@ -635,6 +658,9 @@
         <v>1</v>
       </c>
       <c r="Q5" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R5" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -679,11 +705,13 @@
         <v>5</v>
       </c>
       <c r="L6" s="0"/>
-      <c r="M6" s="0" t="b">
-        <v>0</v>
+      <c r="M6" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data.csv</t>
+        </is>
       </c>
       <c r="N6" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O6" s="0" t="b">
         <v>1</v>
@@ -692,6 +720,9 @@
         <v>1</v>
       </c>
       <c r="Q6" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R6" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -736,11 +767,13 @@
         <v>6</v>
       </c>
       <c r="L7" s="0"/>
-      <c r="M7" s="0" t="b">
-        <v>0</v>
+      <c r="M7" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data.csv</t>
+        </is>
       </c>
       <c r="N7" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O7" s="0" t="b">
         <v>1</v>
@@ -749,6 +782,9 @@
         <v>1</v>
       </c>
       <c r="Q7" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R7" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -793,11 +829,13 @@
         <v>7</v>
       </c>
       <c r="L8" s="0"/>
-      <c r="M8" s="0" t="b">
-        <v>0</v>
+      <c r="M8" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data.csv</t>
+        </is>
       </c>
       <c r="N8" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O8" s="0" t="b">
         <v>1</v>
@@ -806,6 +844,9 @@
         <v>1</v>
       </c>
       <c r="Q8" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R8" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -850,11 +891,13 @@
         <v>7</v>
       </c>
       <c r="L9" s="0"/>
-      <c r="M9" s="0" t="b">
-        <v>0</v>
+      <c r="M9" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data.csv</t>
+        </is>
       </c>
       <c r="N9" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O9" s="0" t="b">
         <v>1</v>
@@ -863,6 +906,9 @@
         <v>1</v>
       </c>
       <c r="Q9" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R9" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -907,11 +953,13 @@
         <v>7</v>
       </c>
       <c r="L10" s="0"/>
-      <c r="M10" s="0" t="b">
-        <v>0</v>
+      <c r="M10" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data.csv</t>
+        </is>
       </c>
       <c r="N10" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O10" s="0" t="b">
         <v>1</v>
@@ -920,6 +968,9 @@
         <v>1</v>
       </c>
       <c r="Q10" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R10" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -964,19 +1015,24 @@
         <v>8</v>
       </c>
       <c r="L11" s="0"/>
-      <c r="M11" s="0" t="b">
-        <v>0</v>
+      <c r="M11" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data.csv</t>
+        </is>
       </c>
       <c r="N11" s="0" t="b">
         <v>0</v>
       </c>
       <c r="O11" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P11" s="0" t="b">
         <v>1</v>
       </c>
       <c r="Q11" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R11" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1021,19 +1077,24 @@
         <v>9</v>
       </c>
       <c r="L12" s="0"/>
-      <c r="M12" s="0" t="b">
-        <v>0</v>
+      <c r="M12" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data.csv</t>
+        </is>
       </c>
       <c r="N12" s="0" t="b">
         <v>0</v>
       </c>
       <c r="O12" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P12" s="0" t="b">
         <v>1</v>
       </c>
       <c r="Q12" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R12" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1078,19 +1139,24 @@
         <v>11</v>
       </c>
       <c r="L13" s="0"/>
-      <c r="M13" s="0" t="b">
-        <v>0</v>
+      <c r="M13" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data.csv</t>
+        </is>
       </c>
       <c r="N13" s="0" t="b">
         <v>0</v>
       </c>
       <c r="O13" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P13" s="0" t="b">
         <v>1</v>
       </c>
       <c r="Q13" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R13" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1135,19 +1201,24 @@
         <v>11</v>
       </c>
       <c r="L14" s="0"/>
-      <c r="M14" s="0" t="b">
-        <v>0</v>
+      <c r="M14" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data.csv</t>
+        </is>
       </c>
       <c r="N14" s="0" t="b">
         <v>0</v>
       </c>
       <c r="O14" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P14" s="0" t="b">
         <v>1</v>
       </c>
       <c r="Q14" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R14" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1192,19 +1263,24 @@
         <v>11</v>
       </c>
       <c r="L15" s="0"/>
-      <c r="M15" s="0" t="b">
-        <v>0</v>
+      <c r="M15" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data.csv</t>
+        </is>
       </c>
       <c r="N15" s="0" t="b">
         <v>0</v>
       </c>
       <c r="O15" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P15" s="0" t="b">
         <v>1</v>
       </c>
       <c r="Q15" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R15" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1249,19 +1325,24 @@
         <v>12</v>
       </c>
       <c r="L16" s="0"/>
-      <c r="M16" s="0" t="b">
-        <v>0</v>
+      <c r="M16" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data.csv</t>
+        </is>
       </c>
       <c r="N16" s="0" t="b">
         <v>0</v>
       </c>
       <c r="O16" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P16" s="0" t="b">
         <v>1</v>
       </c>
       <c r="Q16" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="R16" s="0" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1294,11 +1375,16 @@
       <c r="L17" s="0" t="n">
         <v>40</v>
       </c>
-      <c r="M17" s="0"/>
+      <c r="M17" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data.csv</t>
+        </is>
+      </c>
       <c r="N17" s="0"/>
       <c r="O17" s="0"/>
       <c r="P17" s="0"/>
       <c r="Q17" s="0"/>
+      <c r="R17" s="0"/>
     </row>
     <row r="18">
       <c r="A18" s="0" t="inlineStr">
@@ -1329,11 +1415,16 @@
       <c r="L18" s="0" t="n">
         <v>38</v>
       </c>
-      <c r="M18" s="0"/>
+      <c r="M18" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data.csv</t>
+        </is>
+      </c>
       <c r="N18" s="0"/>
       <c r="O18" s="0"/>
       <c r="P18" s="0"/>
       <c r="Q18" s="0"/>
+      <c r="R18" s="0"/>
     </row>
     <row r="19">
       <c r="A19" s="0" t="inlineStr">
@@ -1364,11 +1455,16 @@
       <c r="L19" s="0" t="n">
         <v>36</v>
       </c>
-      <c r="M19" s="0"/>
+      <c r="M19" s="0" t="inlineStr">
+        <is>
+          <t>file:///home/cbroult/work/ruby/predictability-engine/data/samples/sample_data.csv</t>
+        </is>
+      </c>
       <c r="N19" s="0"/>
       <c r="O19" s="0"/>
       <c r="P19" s="0"/>
       <c r="Q19" s="0"/>
+      <c r="R19" s="0"/>
     </row>
   </sheetData>
   <sheetCalcPr fullCalcOnLoad="1"/>

--- a/data/samples/reports/sample_data/dashboard.xlsx
+++ b/data/samples/reports/sample_data/dashboard.xlsx
@@ -1373,7 +1373,7 @@
       <c r="J17" s="0"/>
       <c r="K17" s="0"/>
       <c r="L17" s="0" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M17" s="0" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
       <c r="J18" s="0"/>
       <c r="K18" s="0"/>
       <c r="L18" s="0" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M18" s="0" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
       <c r="J19" s="0"/>
       <c r="K19" s="0"/>
       <c r="L19" s="0" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M19" s="0" t="inlineStr">
         <is>

--- a/data/samples/reports/sample_data/dashboard.xlsx
+++ b/data/samples/reports/sample_data/dashboard.xlsx
@@ -1373,7 +1373,7 @@
       <c r="J17" s="0"/>
       <c r="K17" s="0"/>
       <c r="L17" s="0" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M17" s="0" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
       <c r="J18" s="0"/>
       <c r="K18" s="0"/>
       <c r="L18" s="0" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M18" s="0" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
       <c r="J19" s="0"/>
       <c r="K19" s="0"/>
       <c r="L19" s="0" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M19" s="0" t="inlineStr">
         <is>

--- a/data/samples/reports/sample_data/dashboard.xlsx
+++ b/data/samples/reports/sample_data/dashboard.xlsx
@@ -1373,7 +1373,7 @@
       <c r="J17" s="0"/>
       <c r="K17" s="0"/>
       <c r="L17" s="0" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M17" s="0" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
       <c r="J18" s="0"/>
       <c r="K18" s="0"/>
       <c r="L18" s="0" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M18" s="0" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
       <c r="J19" s="0"/>
       <c r="K19" s="0"/>
       <c r="L19" s="0" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M19" s="0" t="inlineStr">
         <is>

--- a/data/samples/reports/sample_data/dashboard.xlsx
+++ b/data/samples/reports/sample_data/dashboard.xlsx
@@ -1373,7 +1373,7 @@
       <c r="J17" s="0"/>
       <c r="K17" s="0"/>
       <c r="L17" s="0" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M17" s="0" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
       <c r="J18" s="0"/>
       <c r="K18" s="0"/>
       <c r="L18" s="0" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M18" s="0" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
       <c r="J19" s="0"/>
       <c r="K19" s="0"/>
       <c r="L19" s="0" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M19" s="0" t="inlineStr">
         <is>

--- a/data/samples/reports/sample_data/dashboard.xlsx
+++ b/data/samples/reports/sample_data/dashboard.xlsx
@@ -1373,7 +1373,7 @@
       <c r="J17" s="0"/>
       <c r="K17" s="0"/>
       <c r="L17" s="0" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M17" s="0" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
       <c r="J18" s="0"/>
       <c r="K18" s="0"/>
       <c r="L18" s="0" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M18" s="0" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
       <c r="J19" s="0"/>
       <c r="K19" s="0"/>
       <c r="L19" s="0" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M19" s="0" t="inlineStr">
         <is>

--- a/data/samples/reports/sample_data/dashboard.xlsx
+++ b/data/samples/reports/sample_data/dashboard.xlsx
@@ -1373,7 +1373,7 @@
       <c r="J17" s="0"/>
       <c r="K17" s="0"/>
       <c r="L17" s="0" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M17" s="0" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
       <c r="J18" s="0"/>
       <c r="K18" s="0"/>
       <c r="L18" s="0" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M18" s="0" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
       <c r="J19" s="0"/>
       <c r="K19" s="0"/>
       <c r="L19" s="0" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M19" s="0" t="inlineStr">
         <is>

--- a/data/samples/reports/sample_data/dashboard.xlsx
+++ b/data/samples/reports/sample_data/dashboard.xlsx
@@ -1373,7 +1373,7 @@
       <c r="J17" s="0"/>
       <c r="K17" s="0"/>
       <c r="L17" s="0" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M17" s="0" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
       <c r="J18" s="0"/>
       <c r="K18" s="0"/>
       <c r="L18" s="0" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M18" s="0" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
       <c r="J19" s="0"/>
       <c r="K19" s="0"/>
       <c r="L19" s="0" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M19" s="0" t="inlineStr">
         <is>

--- a/data/samples/reports/sample_data/dashboard.xlsx
+++ b/data/samples/reports/sample_data/dashboard.xlsx
@@ -1373,7 +1373,7 @@
       <c r="J17" s="0"/>
       <c r="K17" s="0"/>
       <c r="L17" s="0" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M17" s="0" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
       <c r="J18" s="0"/>
       <c r="K18" s="0"/>
       <c r="L18" s="0" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M18" s="0" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
       <c r="J19" s="0"/>
       <c r="K19" s="0"/>
       <c r="L19" s="0" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M19" s="0" t="inlineStr">
         <is>

--- a/data/samples/reports/sample_data/dashboard.xlsx
+++ b/data/samples/reports/sample_data/dashboard.xlsx
@@ -1373,7 +1373,7 @@
       <c r="J17" s="0"/>
       <c r="K17" s="0"/>
       <c r="L17" s="0" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="M17" s="0" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
       <c r="J18" s="0"/>
       <c r="K18" s="0"/>
       <c r="L18" s="0" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M18" s="0" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
       <c r="J19" s="0"/>
       <c r="K19" s="0"/>
       <c r="L19" s="0" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M19" s="0" t="inlineStr">
         <is>

--- a/data/samples/reports/sample_data/dashboard.xlsx
+++ b/data/samples/reports/sample_data/dashboard.xlsx
@@ -1373,7 +1373,7 @@
       <c r="J17" s="0"/>
       <c r="K17" s="0"/>
       <c r="L17" s="0" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="M17" s="0" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
       <c r="J18" s="0"/>
       <c r="K18" s="0"/>
       <c r="L18" s="0" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M18" s="0" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
       <c r="J19" s="0"/>
       <c r="K19" s="0"/>
       <c r="L19" s="0" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M19" s="0" t="inlineStr">
         <is>

--- a/data/samples/reports/sample_data/dashboard.xlsx
+++ b/data/samples/reports/sample_data/dashboard.xlsx
@@ -1373,7 +1373,7 @@
       <c r="J17" s="0"/>
       <c r="K17" s="0"/>
       <c r="L17" s="0" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M17" s="0" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
       <c r="J18" s="0"/>
       <c r="K18" s="0"/>
       <c r="L18" s="0" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="M18" s="0" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
       <c r="J19" s="0"/>
       <c r="K19" s="0"/>
       <c r="L19" s="0" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M19" s="0" t="inlineStr">
         <is>
